--- a/data/信用债发行汇总_2026-09-21.xlsx
+++ b/data/信用债发行汇总_2026-09-21.xlsx
@@ -12671,7 +12671,9 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -13392,7 +13394,11 @@
           <t>26联发集MTN003</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>102683764.IB</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>3+3+1</t>
@@ -13750,10 +13756,14 @@
           <t>26安阳钢铁MTN006(科创债)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>102683767.IB</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>371天+1年+1年+1年</t>
+          <t>1.0164+1+1+1</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -13917,7 +13927,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -14102,7 +14114,11 @@
           <t>26保利发展MTN001B</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>102683773.IB</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -14261,7 +14277,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -14618,7 +14636,11 @@
           <t>26河南路桥MTN002</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>102690049.IB</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -14970,7 +14992,11 @@
           <t>26中国平煤MTN009</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>102683768.IB</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>3+N</t>
@@ -15320,7 +15346,11 @@
           <t>26山东港口MTN005(绿色)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>102683766.IB</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -15659,7 +15689,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AN20" s="2" t="inlineStr"/>
+      <c r="AN20" s="2" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -15844,7 +15876,11 @@
           <t>26保利发展MTN001A</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>102683772.IB</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -16007,7 +16043,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AN22" s="2" t="inlineStr"/>
+      <c r="AN22" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -16020,7 +16058,11 @@
           <t>26厦门海翼MTN002</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>102683749.IB</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -16183,7 +16225,9 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="AN23" s="2" t="inlineStr"/>
+      <c r="AN23" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -16537,56 +16581,56 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>26兴锦01</t>
+          <t>26鄂交04</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>284065.SH</t>
+          <t>525024.SZ</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2.34</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>成都市兴锦城市建设投资有限责任公司</t>
+          <t>湖北交通投资集团有限公司</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>20兴锦01</t>
+          <t>25鄂交02</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1.02Y</t>
+          <t>8.60Y</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>2.0034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16596,20 +16640,20 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>成都兴锦建设投资集团有限责任公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -16622,22 +16666,22 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>成都市兴锦城市建设投资有限责任公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>湖北交通投资集团有限公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
+          <t>2036-09-22</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr"/>
@@ -16654,12 +16698,12 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AE26" s="2" t="inlineStr">
@@ -16669,23 +16713,23 @@
       </c>
       <c r="AF26" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AG26" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AH26" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AI26" s="2" t="inlineStr"/>
       <c r="AJ26" s="2" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AK26" s="2" t="inlineStr">
@@ -16713,56 +16757,56 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>26鄂交04</t>
+          <t>26兴锦01</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>525024.SZ</t>
+          <t>284065.SH</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>10</v>
+        <v>2.34</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>湖北交通投资集团有限公司</t>
+          <t>成都市兴锦城市建设投资有限责任公司</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25鄂交02</t>
+          <t>20兴锦01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8.60Y</t>
+          <t>1.02Y</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2.0034</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16772,20 +16816,20 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr"/>
+          <t>广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>成都兴锦建设投资集团有限责任公司</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -16798,29 +16842,29 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>湖北交通投资集团有限公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)</t>
+          <t>成都市兴锦城市建设投资有限责任公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2036-09-22</t>
+          <t>2031-09-22</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -16830,12 +16874,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE27" s="2" t="inlineStr">
@@ -16845,23 +16889,23 @@
       </c>
       <c r="AF27" s="2" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AG27" s="2" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AH27" s="2" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AI27" s="2" t="inlineStr"/>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AK27" s="2" t="inlineStr">
@@ -17861,7 +17905,9 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -18607,7 +18653,11 @@
           <t>26联发集MTN003</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>102683764.IB</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>3+3+1</t>
@@ -18975,10 +19025,14 @@
           <t>26安阳钢铁MTN006(科创债)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>102683767.IB</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>371天+1年+1年+1年</t>
+          <t>1.0164+1+1+1</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -19142,7 +19196,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -19337,7 +19393,11 @@
           <t>26保利发展MTN001B</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>102683773.IB</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -19496,7 +19556,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -19868,7 +19930,11 @@
           <t>26河南路桥MTN002</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>102690049.IB</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -20230,7 +20296,11 @@
           <t>26中国平煤MTN009</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>102683768.IB</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>3+N</t>
@@ -20590,7 +20660,11 @@
           <t>26山东港口MTN005(绿色)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>102683766.IB</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -20934,7 +21008,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -21129,7 +21205,11 @@
           <t>26保利发展MTN001A</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>102683772.IB</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -21292,7 +21372,9 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -21310,7 +21392,11 @@
           <t>26厦门海翼MTN002</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>102683749.IB</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -21473,7 +21559,9 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="AO23" s="2" t="inlineStr"/>
+      <c r="AO23" s="2" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -21842,56 +21930,56 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>26兴锦01</t>
+          <t>26鄂交04</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>284065.SH</t>
+          <t>525024.SZ</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>2.34</v>
+        <v>10</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>成都市兴锦城市建设投资有限责任公司</t>
+          <t>湖北交通投资集团有限公司</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20兴锦01</t>
+          <t>25鄂交02</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1.02Y</t>
+          <t>8.60Y</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>2.0034</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -21901,20 +21989,20 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>成都兴锦建设投资集团有限责任公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -21927,22 +22015,22 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>成都市兴锦城市建设投资有限责任公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>湖北交通投资集团有限公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
+          <t>2036-09-22</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr"/>
@@ -21959,12 +22047,12 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AE26" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AF26" s="2" t="inlineStr">
@@ -21974,23 +22062,23 @@
       </c>
       <c r="AG26" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AH26" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AI26" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AJ26" s="2" t="inlineStr"/>
       <c r="AK26" s="2" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AL26" s="2" t="inlineStr">
@@ -22023,56 +22111,56 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26鄂交04</t>
+          <t>26兴锦01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>525024.SZ</t>
+          <t>284065.SH</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>10</v>
+        <v>2.34</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>湖北交通投资集团有限公司</t>
+          <t>成都市兴锦城市建设投资有限责任公司</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25鄂交02</t>
+          <t>20兴锦01</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8.60Y</t>
+          <t>1.02Y</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2.0034</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -22082,20 +22170,20 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,平安证券股份有限公司,国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr"/>
+          <t>广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>成都兴锦建设投资集团有限责任公司</t>
+        </is>
+      </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -22108,29 +22196,29 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>湖北交通投资集团有限公司2026年面向专业投资者公开发行公司债券(第一期)(品种二)</t>
+          <t>成都市兴锦城市建设投资有限责任公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>2036-09-22</t>
+          <t>2031-09-22</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="inlineStr"/>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -22140,12 +22228,12 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AE27" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF27" s="2" t="inlineStr">
@@ -22155,23 +22243,23 @@
       </c>
       <c r="AG27" s="2" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AH27" s="2" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AI27" s="2" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AJ27" s="2" t="inlineStr"/>
       <c r="AK27" s="2" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AL27" s="2" t="inlineStr">
@@ -30834,63 +30922,63 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>09-16 19:00</t>
+          <t>09-16 18:00</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>26菏投F1</t>
+          <t>26津渤海MTN014</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>284038.SH</t>
+          <t>102683675.IB</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.90 ~ 2.50</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>山东菏建国有资本投资有限公司</t>
+          <t>天津渤海国有资产经营管理有限公司</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>山东省-菏泽市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>25菏投05</t>
+          <t>26津渤海MTN013</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>4.04Y</t>
+          <t>1.99Y</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>2.1656</t>
+          <t>2.1563</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -30900,19 +30988,19 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司</t>
+          <t>中信银行股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr"/>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -30922,28 +31010,32 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>山东菏建国有资本投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>天津渤海国有资产经营管理有限公司2026年度第十四期中期票据</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>2031-09-17</t>
-        </is>
-      </c>
-      <c r="Z75" s="2" t="inlineStr"/>
+          <t>2028-09-17</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
@@ -30958,32 +31050,32 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AE75" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF75" s="2" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AG75" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AH75" s="2" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AI75" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AJ75" s="2" t="inlineStr"/>
@@ -31007,7 +31099,9 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AO75" s="2" t="inlineStr"/>
+      <c r="AO75" s="2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -31017,63 +31111,63 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>09-16 18:00</t>
+          <t>09-16 19:00</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>26津渤海MTN014</t>
+          <t>26菏投F1</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>102683675.IB</t>
+          <t>284038.SH</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.50</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>天津渤海国有资产经营管理有限公司</t>
+          <t>山东菏建国有资本投资有限公司</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省-菏泽市</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>26津渤海MTN013</t>
+          <t>25菏投05</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>1.99Y</t>
+          <t>4.04Y</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2.1563</t>
+          <t>2.1656</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -31083,19 +31177,19 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,国信证券股份有限公司</t>
+          <t>国投证券股份有限公司</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr"/>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -31105,32 +31199,28 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>天津渤海国有资产经营管理有限公司2026年度第十四期中期票据</t>
+          <t>山东菏建国有资本投资有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>2028-09-17</t>
-        </is>
-      </c>
-      <c r="Z76" s="2" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-17</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr"/>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -31145,32 +31235,32 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AE76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF76" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AG76" s="2" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AH76" s="2" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AI76" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AJ76" s="2" t="inlineStr"/>
@@ -31194,9 +31284,7 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="AO76" s="2" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AO76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
